--- a/PRD.xlsx
+++ b/PRD.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="8280" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Backend Routes" sheetId="1" r:id="rId1"/>
+    <sheet name="Frontend Routes" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Backend Routes'!$A$1:$I$31</definedName>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="100">
   <si>
     <t>Backend Routes</t>
   </si>
@@ -185,6 +186,9 @@
     <t>get all tickets</t>
   </si>
   <si>
+    <t>reporter not included</t>
+  </si>
+  <si>
     <t>create ticket</t>
   </si>
   <si>
@@ -249,6 +253,84 @@
   </si>
   <si>
     <t>update the points in kt for workgroup</t>
+  </si>
+  <si>
+    <t>Models</t>
+  </si>
+  <si>
+    <t>Pages</t>
+  </si>
+  <si>
+    <t>Backend API Call</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Components</t>
+  </si>
+  <si>
+    <t>CreateUser</t>
+  </si>
+  <si>
+    <t>LoginUser</t>
+  </si>
+  <si>
+    <t>GetUser</t>
+  </si>
+  <si>
+    <t>UpdateUser</t>
+  </si>
+  <si>
+    <t>DeleteUser</t>
+  </si>
+  <si>
+    <t>AddLink</t>
+  </si>
+  <si>
+    <t>GetLinks</t>
+  </si>
+  <si>
+    <t>UpdateLink</t>
+  </si>
+  <si>
+    <t>DeleteLink</t>
+  </si>
+  <si>
+    <t>AddTodo</t>
+  </si>
+  <si>
+    <t>UpdateTodo</t>
+  </si>
+  <si>
+    <t>DeleteTodo</t>
+  </si>
+  <si>
+    <t>CreateTicket</t>
+  </si>
+  <si>
+    <t>GetTickets</t>
+  </si>
+  <si>
+    <t>UpdateTickets</t>
+  </si>
+  <si>
+    <t>DeleteTickets</t>
+  </si>
+  <si>
+    <t>CreateHandover</t>
+  </si>
+  <si>
+    <t>AcknowlegeHandover</t>
+  </si>
+  <si>
+    <t>DuplicateHandover</t>
+  </si>
+  <si>
+    <t>UpdateHandover</t>
+  </si>
+  <si>
+    <t>DeleteHandover</t>
   </si>
 </sst>
 </file>
@@ -961,19 +1043,37 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -998,37 +1098,13 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1594,11 +1670,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="9.55555555555556" customWidth="1"/>
-    <col min="3" max="3" width="9.11111111111111" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.11111111111111" style="8" customWidth="1"/>
     <col min="4" max="4" width="40.2222222222222" customWidth="1"/>
     <col min="5" max="5" width="9.55555555555556" customWidth="1"/>
     <col min="6" max="6" width="50.2222222222222" customWidth="1"/>
@@ -1608,635 +1684,638 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.8" spans="1:9">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="5">
+      <c r="A3" s="11">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="25" t="s">
+      <c r="I3" s="23" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="6" t="s">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="7" t="s">
+      <c r="E4" s="14"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="26"/>
+      <c r="I4" s="24"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="6" t="s">
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="7" t="s">
+      <c r="E5" s="14"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="26"/>
+      <c r="I5" s="24"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="6" t="s">
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="7" t="s">
+      <c r="E6" s="14"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="27"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="5">
+      <c r="A7" s="11">
         <v>2</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="5" t="s">
+      <c r="E7" s="14"/>
+      <c r="F7" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="28" t="s">
+      <c r="I7" s="26" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="6" t="s">
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="7" t="s">
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="29"/>
+      <c r="I8" s="27"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="6" t="s">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="7" t="s">
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="I9" s="29"/>
+      <c r="I9" s="27"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="6" t="s">
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="7" t="s">
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="I10" s="29"/>
+      <c r="I10" s="27"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="6" t="s">
+      <c r="A11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="7" t="s">
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="I11" s="30"/>
+      <c r="I11" s="28"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="5">
+      <c r="A12" s="11">
         <v>3</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="I12" s="31" t="s">
+      <c r="I12" s="29" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="6" t="s">
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="7" t="s">
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="I13" s="31"/>
+      <c r="I13" s="29"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="6" t="s">
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="7" t="s">
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="6"/>
-      <c r="I14" s="31"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="29"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="6" t="s">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="12" t="s">
         <v>10</v>
       </c>
       <c r="D15" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="7" t="s">
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="H15" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="I15" s="31"/>
+      <c r="I15" s="29"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="6" t="s">
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="12" t="s">
         <v>10</v>
       </c>
       <c r="D16" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="7" t="s">
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="I16" s="31"/>
+      <c r="I16" s="29"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="10" t="s">
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D17" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="H17" s="10"/>
-      <c r="I17" s="5"/>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="12">
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="H17" s="16"/>
+      <c r="I17" s="11"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="7">
         <v>4</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="13"/>
-      <c r="G18" s="7" t="s">
+      <c r="F18" s="11"/>
+      <c r="G18" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="H18" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="I18" s="31" t="s">
-        <v>39</v>
+      <c r="I18" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="J18" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="6" t="s">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="E19" s="12"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="16" t="s">
+      <c r="E19" s="7"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="I19" s="31"/>
+      <c r="H19" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="I19" s="29"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="6" t="s">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="17" t="s">
+      <c r="D20" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="H20" s="14" t="s">
+      <c r="E20" s="7"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="I20" s="12"/>
+      <c r="H20" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="I20" s="7"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="6" t="s">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="E21" s="12"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="16" t="s">
+      <c r="D21" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="7"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="H21" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="I21" s="31"/>
+      <c r="H21" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="I21" s="29"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="19">
+      <c r="A22" s="7">
         <v>5</v>
       </c>
-      <c r="B22" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="6" t="s">
+      <c r="B22" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D22" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="E22" s="21" t="s">
+      <c r="D22" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="F22" s="21"/>
-      <c r="G22" s="22" t="s">
+      <c r="E22" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" s="7"/>
+      <c r="G22" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="H22" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="I22" s="32" t="s">
+      <c r="H22" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="I22" s="30" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="6" t="s">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="22" t="s">
+      <c r="D23" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="H23" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="I23" s="32"/>
+      <c r="H23" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="I23" s="30"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="6" t="s">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="22" t="s">
+      <c r="D24" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="H24" s="20" t="s">
+      <c r="H24" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="I24" s="30"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="I24" s="32"/>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="6" t="s">
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="I25" s="30"/>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="I26" s="30"/>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="7">
+        <v>6</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F27" s="18"/>
+      <c r="G27" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="H27" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="I27" s="23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="E28" s="7"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="I28" s="23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E29" s="7"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="I29" s="23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E30" s="7"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="I25" s="32"/>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="I26" s="32"/>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="21">
-        <v>6</v>
-      </c>
-      <c r="B27" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="E27" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="F27" s="20"/>
-      <c r="G27" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="H27" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I27" s="25" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="21"/>
-      <c r="B28" s="21"/>
-      <c r="C28" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="E28" s="21"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I28" s="25" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="21"/>
-      <c r="B29" s="21"/>
-      <c r="C29" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="E29" s="21"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="I29" s="25" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="21"/>
-      <c r="B30" s="21"/>
-      <c r="C30" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="E30" s="21"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="25" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="21"/>
-      <c r="B31" s="21"/>
-      <c r="C31" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="25" t="s">
+      <c r="D31" s="18"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="23" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2275,4 +2354,505 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="6.33333333333333" customWidth="1"/>
+    <col min="2" max="2" width="10.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="20.5555555555556" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.4444444444444" customWidth="1"/>
+    <col min="5" max="5" width="11.2222222222222" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="8.88888888888889" customWidth="1"/>
+    <col min="8" max="8" width="12.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="19.8" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="7">
+        <v>2</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="7">
+        <v>3</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="7">
+        <v>4</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="7">
+        <v>5</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="7">
+        <v>6</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="5"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="A13:A18"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A23:A27"/>
+    <mergeCell ref="A28:A32"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="B23:B27"/>
+    <mergeCell ref="B28:B32"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>